--- a/results/02_taxa_assemblage/LDA_Method/ModelC_Weighted/artifacts/training_weights.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelC_Weighted/artifacts/training_weights.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.207708831576254</v>
+        <v>0.3404407543448494</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.42775575759446</v>
+        <v>2.666310623627961</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8373949349333958</v>
+        <v>0.2096872840624322</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3888461395970747</v>
+        <v>0.2588983871463814</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.752582670941512</v>
+        <v>1.784950781636385</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.767945083936907</v>
+        <v>2.981947824886332</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3496409897988013</v>
+        <v>0.7629449302913383</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.757980457734229</v>
+        <v>2.495931550994714</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.191461900257933</v>
+        <v>0.9564671538937354</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.752353028921366</v>
+        <v>3.028073600198286</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.751979366999973</v>
+        <v>2.914708768181651</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.025822252974357</v>
+        <v>0.2826763339785591</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.144221239007055</v>
+        <v>0.1852958794504528</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.181325180777689</v>
+        <v>0.9817373463146232</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.730571954864671</v>
+        <v>2.239244818166248</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8261864634309731</v>
+        <v>0.5326339127680602</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.765959978000378</v>
+        <v>3.119136064127804</v>
       </c>
     </row>
     <row r="19">
@@ -617,277 +617,307 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3269569604993183</v>
+        <v>0.7784472409370002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1507432869786511</v>
+        <v>0.1485414971899061</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.776100674682179</v>
+        <v>0.1240579697670867</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8417318074291837</v>
+        <v>3.093727654334361</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8698258650188675</v>
+        <v>0.9368878724498164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5251797476040035</v>
+        <v>0.6985246173688884</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8155826441500762</v>
+        <v>0.6863689214024996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.184563411566497</v>
+        <v>0.9315583583282567</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6818995559607646</v>
+        <v>0.7668635277606688</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5365007828069441</v>
+        <v>0.4758230417541116</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8200803000737809</v>
+        <v>1.009281093850955</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.333964837483583</v>
+        <v>0.9371024000914965</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.221114250083917</v>
+        <v>1.014132657646792</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.232531481305242</v>
+        <v>0.7176932556148133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.140647867850962</v>
+        <v>0.7006581265430921</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.173194594228025</v>
+        <v>0.9862130619717708</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.225480072341521</v>
+        <v>0.8830621651704349</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.525012921856563</v>
+        <v>0.919663391682107</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.38430614359026</v>
+        <v>0.5815057712087736</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6332982779884249</v>
+        <v>0.8428195649858277</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.373179632483779</v>
+        <v>0.2000472989414895</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8479911226519901</v>
+        <v>0.6540161395249384</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6805663542755616</v>
+        <v>0.3979099273944162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.198376796304837</v>
+        <v>0.8916615251244305</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.433881260945165</v>
+        <v>0.5502233038991322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.181524601064925</v>
+        <v>0.5003509396129751</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.826332364021679</v>
+        <v>0.866644377864869</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
+          <t>S74</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.9221046596688497</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>S79</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.445703178267613</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.9122665037114662</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
           <t>S81</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1.19672160165015</v>
+      <c r="B49" t="n">
+        <v>0.3485600061152054</v>
       </c>
     </row>
   </sheetData>
